--- a/src/attributions/attributions_ig_traj_93.xlsx
+++ b/src/attributions/attributions_ig_traj_93.xlsx
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.09639632036590691</v>
+        <v>0.02380275027598162</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1011,25 +1011,25 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.00298018404442003</v>
+        <v>-0.008811141941207997</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01441396359685988</v>
+        <v>-0.004511143525648143</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1424723877260029</v>
+        <v>0.07336926440543173</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.006797610697870602</v>
+        <v>-0.03530900041866851</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1050,67 +1050,67 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.07227280054887694</v>
+        <v>-0.01316322308066914</v>
       </c>
       <c r="S2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.09075057563050053</v>
+        <v>0.01419416017913605</v>
       </c>
       <c r="U2" t="n">
         <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.06037038222059783</v>
+        <v>-0.03041850612161649</v>
       </c>
       <c r="X2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
         <v>-0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0003319547178251258</v>
+        <v>-0.002960056489862578</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.02721495781313775</v>
+        <v>-0.007930826004094593</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.01877538699580729</v>
+        <v>-0.009250000075072517</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.003398521966829184</v>
+        <v>0.004079674044737715</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.05589691735515379</v>
+        <v>0.02216154462450964</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
@@ -1119,34 +1119,34 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.01041234654168987</v>
+        <v>-0.004028552313951872</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0.03622120773862055</v>
+        <v>-0.0009043839728031424</v>
       </c>
       <c r="AT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.3539917689156694</v>
+        <v>0.125611942386731</v>
       </c>
       <c r="AV2" t="n">
         <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.209249040329009</v>
+        <v>-0.03230395866924059</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -1155,16 +1155,16 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0.05302056356359994</v>
+        <v>-0.0008434292374435404</v>
       </c>
       <c r="BC2" t="n">
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.009728365947649227</v>
+        <v>-0.01005487940030545</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.06053646567642312</v>
+        <v>-0.0170617450192208</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1182,52 +1182,52 @@
         <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0.06870452579525872</v>
+        <v>-0.02192404079866875</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.0444202697377908</v>
+        <v>0.01960554713327745</v>
       </c>
       <c r="BN2" t="n">
         <v>-0</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.161433983957322</v>
+        <v>0.0484365706217046</v>
       </c>
       <c r="BQ2" t="n">
         <v>-0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.04979261515466003</v>
+        <v>0.01830896497930759</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.1851666048358887</v>
+        <v>0.0649232802125685</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.008450836405853744</v>
+        <v>-0.02837794098225545</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1236,55 +1236,55 @@
         <v>-0</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.03826788142335267</v>
+        <v>-0.0141823689371142</v>
       </c>
       <c r="CD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.07967965411672451</v>
+        <v>-0.03047631824653536</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
         <v>0</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.004554012242682317</v>
+        <v>0.0142328943876878</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
         <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.04753701052546468</v>
+        <v>0.01470661766049047</v>
       </c>
       <c r="CM2" t="n">
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.005495143191857639</v>
+        <v>-0.01259560817969113</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.02002077329084174</v>
+        <v>0.002507448260526198</v>
       </c>
       <c r="CR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS2" t="n">
         <v>-0</v>
@@ -1293,13 +1293,13 @@
         <v>0</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.001153638122220646</v>
+        <v>0.001712695180541644</v>
       </c>
       <c r="CV2" t="n">
         <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.0866235788662528</v>
+        <v>-0.03027211249350683</v>
       </c>
       <c r="CX2" t="n">
         <v>0</v>
@@ -1308,52 +1308,52 @@
         <v>0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.01114000160486485</v>
+        <v>0.008747462206016672</v>
       </c>
       <c r="DA2" t="n">
         <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.02918249438456957</v>
+        <v>0.01644088646795431</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.0838162653361505</v>
+        <v>-0.05850371062364856</v>
       </c>
       <c r="DG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH2" t="n">
         <v>0</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.0419619743189457</v>
+        <v>0.004255355890911333</v>
       </c>
       <c r="DJ2" t="n">
         <v>-0</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.01675211757400693</v>
+        <v>0.002362338107706129</v>
       </c>
       <c r="DN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.02552037347344914</v>
+        <v>-0.01562298472121424</v>
       </c>
       <c r="DP2" t="n">
         <v>0</v>
@@ -1362,37 +1362,37 @@
         <v>0</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.04855406192127892</v>
+        <v>0.01787297372189918</v>
       </c>
       <c r="DS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0.006463591028719182</v>
+        <v>0.01445777813436669</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.1367998451560475</v>
+        <v>-0.01476334023662</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.026116885826125</v>
+        <v>-0.02336820711471279</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
@@ -1401,13 +1401,13 @@
         <v>-0</v>
       </c>
       <c r="EE2" t="n">
-        <v>-0.05046860768371882</v>
+        <v>-0.0002826399918018231</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.07496193414483206</v>
+        <v>-0.02473703389740277</v>
       </c>
       <c r="EH2" t="n">
         <v>-0</v>
@@ -1416,79 +1416,79 @@
         <v>0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.01496353731080941</v>
+        <v>-0.002973960720344088</v>
       </c>
       <c r="EK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL2" t="n">
         <v>-0</v>
       </c>
       <c r="EM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.08883331746331807</v>
+        <v>0.0132442816234706</v>
       </c>
       <c r="EO2" t="n">
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.06477583364532737</v>
+        <v>-0.008571323976531214</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER2" t="n">
         <v>-0</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.02468297761685942</v>
+        <v>0.01497498880968384</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.07168766982136131</v>
+        <v>0.01557416398892963</v>
       </c>
       <c r="EX2" t="n">
         <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0.09223881124638246</v>
+        <v>-0.04097404762092158</v>
       </c>
       <c r="EZ2" t="n">
         <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.00310796149683126</v>
+        <v>0.007776245500779482</v>
       </c>
       <c r="FC2" t="n">
         <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
         <v>0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.03088480296567875</v>
+        <v>0.01426586525863212</v>
       </c>
       <c r="FG2" t="n">
         <v>0</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.002291788102156819</v>
+        <v>0.03352337436802185</v>
       </c>
       <c r="FI2" t="n">
         <v>-0</v>
@@ -1497,10 +1497,10 @@
         <v>-0</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.06924623645149494</v>
+        <v>-0.01340123821675362</v>
       </c>
       <c r="FL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM2" t="n">
         <v>0</v>
@@ -1509,13 +1509,13 @@
         <v>0</v>
       </c>
       <c r="FO2" t="n">
-        <v>-0.01052850256590171</v>
+        <v>0.02507795723952983</v>
       </c>
       <c r="FP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.01388731450379597</v>
+        <v>-0.007847867570647067</v>
       </c>
       <c r="FR2" t="n">
         <v>-0</v>
@@ -1524,7 +1524,7 @@
         <v>-0</v>
       </c>
       <c r="FT2" t="n">
-        <v>-0.003938995165453105</v>
+        <v>0.009168374356401271</v>
       </c>
       <c r="FU2" t="n">
         <v>-0</v>
@@ -1536,13 +1536,13 @@
         <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0.02788816274229586</v>
+        <v>0.002954251688491999</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.05512442808457767</v>
+        <v>-0.01914345232323546</v>
       </c>
       <c r="GA2" t="n">
         <v>0</v>
@@ -1551,10 +1551,10 @@
         <v>-0</v>
       </c>
       <c r="GC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE2" t="n">
         <v>-0</v>
@@ -1563,7 +1563,7 @@
         <v>-0</v>
       </c>
       <c r="GG2" t="n">
-        <v>-0.0848089349667914</v>
+        <v>-0.01006102363017148</v>
       </c>
     </row>
     <row r="3">
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1962679947953559</v>
+        <v>0.001151677637244838</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -2718,16 +2718,16 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01971052363803886</v>
+        <v>0.0001690628817389839</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.05721191706411369</v>
+        <v>-0.0004195107898785418</v>
       </c>
       <c r="H5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2211619741317052</v>
+        <v>0.003371934271924809</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2745,16 +2745,16 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03431862033659668</v>
+        <v>-7.933667844077036e-05</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.106184923446391</v>
+        <v>-0.001585924290414651</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -2763,115 +2763,115 @@
         <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1019858693604131</v>
+        <v>0.0006071017738215786</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.09508485441591942</v>
+        <v>-0.001814147555896191</v>
       </c>
       <c r="X5" t="n">
         <v>-0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.02705827837076733</v>
+        <v>-0.0003462762448843611</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>-0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.04574761177580101</v>
+        <v>-0.0001796953695719933</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.004894952776640717</v>
+        <v>-0.0001986311960648262</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.006334603264886613</v>
+        <v>-6.859085875511978e-05</v>
       </c>
       <c r="AI5" t="n">
         <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.05120795694701797</v>
+        <v>0.0003305370355720502</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0377013415022558</v>
+        <v>0.000733994659207995</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.06035433968341366</v>
+        <v>-0.000213486195243154</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.4003479692114176</v>
+        <v>0.004882662417235638</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.2222402120437681</v>
+        <v>-0.0003011604532727228</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.181744437218623</v>
+        <v>-0.0005035076251524933</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.04424020896547783</v>
+        <v>-0.0008801349032875454</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,13 +2880,13 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.09784517410042262</v>
+        <v>-0.0007736954946703436</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.0004294992797166536</v>
+        <v>-5.321215525253695e-05</v>
       </c>
       <c r="BJ5" t="n">
         <v>-0</v>
@@ -2895,25 +2895,25 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.05456809571852006</v>
+        <v>0.001133327237560329</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
         <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.05566851150816939</v>
+        <v>0.002291241285375051</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.1061199472847257</v>
+        <v>-0.0005308970431555563</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,49 +2925,49 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1839297000604707</v>
+        <v>0.002363949421692699</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.08779467802337958</v>
+        <v>-0.0002693459189853772</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.08427035688227079</v>
+        <v>-9.358116585376491e-05</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
         <v>-0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.1011755557762469</v>
+        <v>-0.0008147133649868076</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
         <v>-0</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.02915366098290495</v>
+        <v>-0.0001048208711151156</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.04907872952337945</v>
+        <v>0.0004503480219218728</v>
       </c>
       <c r="CK5" t="n">
         <v>-0</v>
@@ -2979,49 +2979,49 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.008189744383435621</v>
+        <v>-0.0007608501295913251</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.02485179284784909</v>
+        <v>0.0002888443324518179</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.006033351443912405</v>
+        <v>-0.0001682634997376722</v>
       </c>
       <c r="CT5" t="n">
         <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
         <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.1024963280001885</v>
+        <v>-0.0009185828167141577</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
         <v>0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.05060727511968968</v>
+        <v>-0.0003512632695374864</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.06168197924051883</v>
+        <v>0.0006798690477830341</v>
       </c>
       <c r="DC5" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.1047873155704423</v>
+        <v>-0.00191468907397125</v>
       </c>
       <c r="DG5" t="n">
         <v>-0</v>
@@ -3042,67 +3042,67 @@
         <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.05580749181889054</v>
+        <v>-0.001686120162567408</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.02025901143496344</v>
+        <v>0.0003757664144838118</v>
       </c>
       <c r="DL5" t="n">
         <v>-0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.008590074995232897</v>
+        <v>-0.000169477426830626</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.02790575813273258</v>
+        <v>-0.0005570996396555587</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.02339607164410816</v>
+        <v>0.001451492950833552</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.1266084160157057</v>
+        <v>-0.0006574403786042923</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.008650843848221887</v>
+        <v>-0.00106101035413222</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.01021171677371917</v>
+        <v>0.0008792445033415045</v>
       </c>
       <c r="ED5" t="n">
         <v>-0</v>
@@ -3114,76 +3114,76 @@
         <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.07888772736970945</v>
+        <v>-0.0007907404986839683</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.004079604141112514</v>
+        <v>-0.0002042800823657182</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.07046850456888747</v>
+        <v>0.0001491467938292426</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
         <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.09318851267697172</v>
+        <v>-0.00017223013311225</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
         <v>-0</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.1194368610764748</v>
+        <v>0.0002425542677840161</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.05182157265819334</v>
+        <v>0.0004396964230872838</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.1087699810157276</v>
+        <v>-0.001301973140391193</v>
       </c>
       <c r="EZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA5" t="n">
         <v>-0</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.06295367310974787</v>
+        <v>-0.0003997806077426768</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.06258492656753695</v>
+        <v>0.0005044110734318104</v>
       </c>
       <c r="FE5" t="n">
         <v>-0</v>
@@ -3192,10 +3192,10 @@
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.008391369980013282</v>
+        <v>0.001097722321177667</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
@@ -3204,25 +3204,25 @@
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.0320199543822343</v>
+        <v>-0.0005732626895879267</v>
       </c>
       <c r="FL5" t="n">
         <v>0</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.003759318893457147</v>
+        <v>-0.0005036018681961082</v>
       </c>
       <c r="FN5" t="n">
         <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
         <v>0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.01322411451710705</v>
+        <v>-3.365477979544203e-05</v>
       </c>
       <c r="FR5" t="n">
         <v>-0</v>
@@ -3231,25 +3231,25 @@
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>-0.0002021997124743214</v>
+        <v>0.000390995062245848</v>
       </c>
       <c r="FU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.06093400548315379</v>
+        <v>0.0002212888910488688</v>
       </c>
       <c r="FW5" t="n">
         <v>-0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
         <v>-0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.05900536811396005</v>
+        <v>-0.0008376437783244385</v>
       </c>
       <c r="GA5" t="n">
         <v>0</v>
@@ -3261,13 +3261,13 @@
         <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
-        <v>-0.0386618498111095</v>
+        <v>0.0005699367685889495</v>
       </c>
       <c r="GF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG5" t="n">
         <v>-0</v>
@@ -3847,19 +3847,19 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4021542758794142</v>
+        <v>0.4260954177712032</v>
       </c>
       <c r="C7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3338033556569747</v>
+        <v>-0.2456227720489691</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.01039914415008003</v>
+        <v>-0.006423913611152056</v>
       </c>
       <c r="F7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>-0</v>
@@ -3874,16 +3874,16 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4256564372280086</v>
+        <v>0.6152085843931197</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.32371758452639</v>
+        <v>-0.3084831544838218</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.08940583601779202</v>
+        <v>-0.1078829514142961</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3898,22 +3898,22 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1993958885518518</v>
+        <v>0.2786076372921691</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.04573695192214769</v>
+        <v>-0.0713572271538726</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1602751503447912</v>
+        <v>-0.01207663067757892</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
@@ -3925,28 +3925,28 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.04315305667798321</v>
+        <v>-0.02813875926117021</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.00789001894454985</v>
+        <v>0.1428823107015298</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.002209769409020455</v>
+        <v>-0.02952968591547709</v>
       </c>
       <c r="AG7" t="n">
         <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
@@ -3955,43 +3955,43 @@
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.04455922316026793</v>
+        <v>0.2565709209688188</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.09465801658516486</v>
+        <v>-0.1586838828105151</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.07688564992870635</v>
+        <v>0.2127296219123044</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
         <v>-0</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.6423708254969364</v>
+        <v>0.7306631347158377</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.1562865029768009</v>
+        <v>-0.3684244207453704</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1641332870019535</v>
+        <v>-0.2485757601181304</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
@@ -4000,25 +4000,25 @@
         <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.07524633265275786</v>
+        <v>-0.006547288752970539</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.1559668978151854</v>
+        <v>-0.1544142634818877</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.1396535662234626</v>
+        <v>-0.09823644033767816</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,7 +4027,7 @@
         <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.09164796527865751</v>
+        <v>-0.07387425879111341</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.05203071090137639</v>
+        <v>0.04050097486295592</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.2106588180821064</v>
+        <v>0.04270443497958334</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
@@ -4063,16 +4063,16 @@
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.3123312378770923</v>
+        <v>0.6143683077278308</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0.07352173248458317</v>
+        <v>-0.1758796557327027</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.1375281854608437</v>
+        <v>-0.03412713976788779</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -4081,85 +4081,85 @@
         <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.1409775268205152</v>
+        <v>-0.2659046324438082</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.06527823786358468</v>
+        <v>0.223781518710392</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.03972071890856987</v>
+        <v>-0.05933991338895563</v>
       </c>
       <c r="CI7" t="n">
         <v>-0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.00924538282201726</v>
+        <v>-0.1999334163190472</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.0937960669408589</v>
+        <v>0.3821519538694087</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.1120095791631889</v>
+        <v>0.1198078177582882</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.1321542516692299</v>
+        <v>-0.2667298031422095</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.1015995599359604</v>
+        <v>0.223117434651268</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.04839798365699768</v>
+        <v>-0.03847379700371782</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
@@ -4171,79 +4171,79 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.1034216962880905</v>
+        <v>-0.4073591821488296</v>
       </c>
       <c r="DG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.07421759518706361</v>
+        <v>0.1252226383914221</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.07366746763353245</v>
+        <v>-0.1061979347713049</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.01052394452493566</v>
+        <v>-0.07928391290955068</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.1063719559628305</v>
+        <v>0.07349367401044996</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.1274259638561785</v>
+        <v>0.02666569368657599</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.04478380658195296</v>
+        <v>0.08815063358142858</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.03507290463087041</v>
+        <v>-0.2178595912334161</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.04499618752960924</v>
+        <v>-0.2583305912074996</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
         <v>-0</v>
@@ -4252,22 +4252,22 @@
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.116684756869816</v>
+        <v>-0.2398596388723229</v>
       </c>
       <c r="EH7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.08874479783606048</v>
+        <v>0.1951426806415611</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.07097318870370242</v>
+        <v>-0.0107225476506323</v>
       </c>
       <c r="EK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
         <v>-0</v>
@@ -4279,22 +4279,22 @@
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.1546777827711787</v>
+        <v>-0.1746141428966348</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.07502561565101103</v>
+        <v>0.06418443470095742</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.01412378056407776</v>
+        <v>0.01225885750698135</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4303,25 +4303,25 @@
         <v>-0</v>
       </c>
       <c r="EX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.1385391594904212</v>
+        <v>-0.3245636770009094</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.07222484590112722</v>
+        <v>0.2749173808324862</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.04432078565576164</v>
+        <v>-0.05263481650007204</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
@@ -4330,19 +4330,19 @@
         <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.04862961878662813</v>
+        <v>-0.203635155770001</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.1234883945811297</v>
+        <v>0.1598044875672545</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.03045383529122688</v>
+        <v>-0.002503404458727573</v>
       </c>
       <c r="FL7" t="n">
         <v>-0</v>
@@ -4351,61 +4351,61 @@
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.02172178784340546</v>
+        <v>-0.04849229910093662</v>
       </c>
       <c r="FR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.08956979197122754</v>
+        <v>0.1173255239705103</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.006598819090206948</v>
+        <v>0.03495030680509638</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX7" t="n">
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.05168571864933833</v>
+        <v>-0.3077474785407019</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.1313714238808838</v>
+        <v>0.1173820335182826</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
         <v>-0</v>
@@ -4416,22 +4416,22 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.3866345650987164</v>
+        <v>0.510134480927237</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0652196549500524</v>
+        <v>-0.02317315160760532</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1852380084651767</v>
+        <v>-0.1253739700437799</v>
       </c>
       <c r="G8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>-0</v>
@@ -4443,25 +4443,25 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3589012147112821</v>
+        <v>0.752245188593158</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.06311468071868366</v>
+        <v>-0.1885508715314557</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3651221592817521</v>
+        <v>-0.1678339080203445</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -4470,7 +4470,7 @@
         <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1094580176934663</v>
+        <v>0.2396801489690978</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -4479,64 +4479,64 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.07493545523177346</v>
+        <v>-0.1550645178228026</v>
       </c>
       <c r="X8" t="n">
-        <v>0.04537530539723772</v>
+        <v>-0.02410377314521068</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
         <v>-0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.02680376375963907</v>
+        <v>0.03359813872090403</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.01825073112775779</v>
+        <v>-0.09489508163883574</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.004488947494421796</v>
+        <v>-0.05287303351191076</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.09532539838076318</v>
+        <v>0.2745333803767226</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.00415580200122351</v>
+        <v>0.1634374728456751</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.1346001625284309</v>
+        <v>-0.2268491839777776</v>
       </c>
       <c r="AQ8" t="n">
         <v>-0</v>
@@ -4548,37 +4548,37 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.5030289018818075</v>
+        <v>1.091220677072524</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.1315890198888514</v>
+        <v>-0.3275860908385788</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.3211154406559409</v>
+        <v>-0.3515073625099807</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC8" t="n">
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.1325088011753167</v>
+        <v>-0.01796814793093769</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -4587,43 +4587,43 @@
         <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.09895809076854709</v>
+        <v>-0.134056749700401</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.06719795290494708</v>
+        <v>-0.0733891101654074</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.1272550426278233</v>
+        <v>0.08137432507660729</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
         <v>-0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.001543428793494194</v>
+        <v>0.1980451508661971</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.02834197504386468</v>
+        <v>0.002663628703968563</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT8" t="n">
         <v>-0</v>
@@ -4632,7 +4632,7 @@
         <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.2521749399794315</v>
+        <v>0.7901966277984974</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
@@ -4641,10 +4641,10 @@
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.09463853581078283</v>
+        <v>-0.1840896908271401</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.1104589849583093</v>
+        <v>-0.2360193733155813</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
@@ -4659,7 +4659,7 @@
         <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.1334336215203771</v>
+        <v>-0.3468040884577288</v>
       </c>
       <c r="CF8" t="n">
         <v>0</v>
@@ -4668,79 +4668,79 @@
         <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.02750903240830612</v>
+        <v>0.05031868348433031</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.1130399748392108</v>
+        <v>0.1550577490887936</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM8" t="n">
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.009208760784757512</v>
+        <v>-0.3777219296855947</v>
       </c>
       <c r="CO8" t="n">
         <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.03142847188632505</v>
+        <v>0.2134092937630619</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.02608865444638875</v>
+        <v>0.2026030393924557</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU8" t="n">
         <v>-0</v>
       </c>
       <c r="CV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.1125354257182475</v>
+        <v>-0.3272563637820126</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
         <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.01881686222551609</v>
+        <v>-0.004107552837681431</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.1285816063493219</v>
+        <v>0.1300902101041123</v>
       </c>
       <c r="DB8" t="n">
         <v>0</v>
       </c>
       <c r="DC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.110943632860503</v>
+        <v>-0.03500019725909333</v>
       </c>
       <c r="DG8" t="n">
         <v>0</v>
@@ -4749,64 +4749,64 @@
         <v>-0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.05924378836863835</v>
+        <v>-0.2640672201424414</v>
       </c>
       <c r="DJ8" t="n">
-        <v>-0.0781327605217683</v>
+        <v>-0.09624444256639834</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
       </c>
       <c r="DL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.02089521938103137</v>
+        <v>-0.1094779538443846</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.004531732174614046</v>
+        <v>-0.02619741750552691</v>
       </c>
       <c r="DS8" t="n">
-        <v>-0.01960440075622137</v>
+        <v>-0.01278670725710491</v>
       </c>
       <c r="DT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW8" t="n">
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.07880764562008102</v>
+        <v>0.1092180431086368</v>
       </c>
       <c r="DY8" t="n">
         <v>0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.03454565964938335</v>
+        <v>-0.07670621588935297</v>
       </c>
       <c r="EB8" t="n">
-        <v>-0.07168398243722526</v>
+        <v>-0.1162607643484133</v>
       </c>
       <c r="EC8" t="n">
         <v>-0</v>
@@ -4818,25 +4818,25 @@
         <v>-0</v>
       </c>
       <c r="EF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.0959036161817763</v>
+        <v>-0.05096223737680315</v>
       </c>
       <c r="EH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.02756057177449348</v>
+        <v>-0.124987042922577</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.1179096359739856</v>
+        <v>0.05247735478366447</v>
       </c>
       <c r="EL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM8" t="n">
         <v>-0</v>
@@ -4845,37 +4845,37 @@
         <v>-0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.05661271075962738</v>
+        <v>-0.1892116993312313</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
         <v>-0</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.03867075363098797</v>
+        <v>-0.1838854599527084</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.07324900669467149</v>
+        <v>0.09719161948642964</v>
       </c>
       <c r="EU8" t="n">
         <v>-0</v>
       </c>
       <c r="EV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX8" t="n">
         <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.1132900553736543</v>
+        <v>-0.3682751544074002</v>
       </c>
       <c r="EZ8" t="n">
         <v>0</v>
@@ -4884,52 +4884,52 @@
         <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.02133329054558526</v>
+        <v>-0.007389888835078848</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.1171610192165286</v>
+        <v>0.1273841842789155</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.0418726762675006</v>
+        <v>-0.3629465976699605</v>
       </c>
       <c r="FI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ8" t="n">
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.04702444470215472</v>
+        <v>0.1994321184170075</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.105048327923058</v>
+        <v>0.130824887462705</v>
       </c>
       <c r="FM8" t="n">
         <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.01636650926019255</v>
+        <v>-0.09421733839058512</v>
       </c>
       <c r="FR8" t="n">
         <v>-0</v>
@@ -4938,28 +4938,28 @@
         <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.0201023470847986</v>
+        <v>0.02573564981085936</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.05561454098591653</v>
+        <v>0.2206606386344299</v>
       </c>
       <c r="FV8" t="n">
         <v>-0</v>
       </c>
       <c r="FW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.01046553829503089</v>
+        <v>-0.1336681604165663</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
         <v>-0</v>
@@ -4968,7 +4968,7 @@
         <v>0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.0923712354584319</v>
+        <v>-0.09527424431893169</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
@@ -4977,7 +4977,7 @@
         <v>-0</v>
       </c>
       <c r="GG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5554,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1171522203616748</v>
+        <v>0.0118820498106034</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -5563,25 +5563,25 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.07769537784154766</v>
+        <v>-0.003253798049857726</v>
       </c>
       <c r="F10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.01403027759955246</v>
+        <v>-0.0009532599433266761</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1072912980289972</v>
+        <v>0.01860293559166539</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -5590,34 +5590,34 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.07166815446829157</v>
+        <v>-0.01029728660843802</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.06128325757120401</v>
+        <v>-0.005690182837547014</v>
       </c>
       <c r="R10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.103369047296544</v>
+        <v>0.008023209479981709</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.05071431191825285</v>
+        <v>-0.009678666572573652</v>
       </c>
       <c r="X10" t="n">
         <v>-0</v>
@@ -5626,25 +5626,25 @@
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.0298550182338729</v>
+        <v>-0.003807520092918035</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.03223041025871016</v>
+        <v>-9.000947345274181e-05</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.02019244749160701</v>
+        <v>-0.001947668249037561</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -5653,43 +5653,43 @@
         <v>-0</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.007086456557502764</v>
+        <v>0.0012691824653067</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.04375141117226868</v>
+        <v>0.006227063616836465</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.02245480314480911</v>
+        <v>-0.0004440062528604215</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.01894393067596725</v>
+        <v>0.0003105117972520375</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT10" t="n">
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.2891945937456054</v>
+        <v>0.02766647119632201</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
@@ -5698,25 +5698,25 @@
         <v>-0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.05339141869602029</v>
+        <v>-0.01238783494660175</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
         <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.06169996504380463</v>
+        <v>-0.00465009440436462</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC10" t="n">
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.04296874510369437</v>
+        <v>-0.004936534986797972</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -5725,25 +5725,25 @@
         <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.1103950561165175</v>
+        <v>-0.007732308112455536</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-0.05456408347896312</v>
+        <v>0.0004802648060774828</v>
       </c>
       <c r="BK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.09259187529615248</v>
+        <v>0.007545786935278249</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
@@ -5752,16 +5752,16 @@
         <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.0350001516013413</v>
+        <v>0.009313971624906697</v>
       </c>
       <c r="BQ10" t="n">
         <v>-0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.01513760181454501</v>
+        <v>0.001756236775046453</v>
       </c>
       <c r="BT10" t="n">
         <v>-0</v>
@@ -5770,34 +5770,34 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.1640321186132099</v>
+        <v>0.0180047122095656</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
         <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.01621721108184061</v>
+        <v>-0.007223275391349716</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.04086317313890904</v>
+        <v>-0.005727109437366726</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.04005039453736143</v>
+        <v>-0.004879085073663173</v>
       </c>
       <c r="CF10" t="n">
         <v>-0</v>
@@ -5806,7 +5806,7 @@
         <v>-0</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.02312623059918093</v>
+        <v>0.002930774584608174</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
@@ -5815,34 +5815,34 @@
         <v>-0</v>
       </c>
       <c r="CK10" t="n">
-        <v>-0.004960154156225826</v>
+        <v>0.0007787635248558353</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.03013559665652524</v>
+        <v>-0.005220958472171077</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.06824728127482101</v>
+        <v>0.009198954450465462</v>
       </c>
       <c r="CR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>-0.008255915511666868</v>
+        <v>0.001853146845881326</v>
       </c>
       <c r="CU10" t="n">
         <v>0</v>
@@ -5851,16 +5851,16 @@
         <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.02617137099424812</v>
+        <v>-0.00472877828929103</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
         <v>0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.008103028067095468</v>
+        <v>0.002461754124577664</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
@@ -5869,34 +5869,34 @@
         <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>-0.004783080777824972</v>
+        <v>0.002859735662625968</v>
       </c>
       <c r="DD10" t="n">
         <v>0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.1341008557642005</v>
+        <v>-6.772133967996211e-05</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.004980297071295224</v>
+        <v>-0.004135368216590594</v>
       </c>
       <c r="DJ10" t="n">
         <v>0</v>
       </c>
       <c r="DK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0.03140617096667465</v>
+        <v>0.0007812014845062532</v>
       </c>
       <c r="DM10" t="n">
         <v>-0</v>
@@ -5905,7 +5905,7 @@
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.01030125214196313</v>
+        <v>-0.005601060091166336</v>
       </c>
       <c r="DP10" t="n">
         <v>-0</v>
@@ -5914,25 +5914,25 @@
         <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.00772217145140657</v>
+        <v>-0.005235341434612828</v>
       </c>
       <c r="DS10" t="n">
         <v>-0</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.00397111530790464</v>
+        <v>0.001547746582648845</v>
       </c>
       <c r="DV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.02986009251632469</v>
+        <v>0.005890664685835044</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
@@ -5941,16 +5941,16 @@
         <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.05060827884281158</v>
+        <v>-0.007929149487226089</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.02463985195862901</v>
+        <v>-0.003472218880915446</v>
       </c>
       <c r="EE10" t="n">
         <v>-0</v>
@@ -5959,16 +5959,16 @@
         <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.001186832841766219</v>
+        <v>-0.000168004159605919</v>
       </c>
       <c r="EH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.05405793045737024</v>
+        <v>-0.003058085590850502</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
@@ -5977,7 +5977,7 @@
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.01132273647538058</v>
+        <v>-0.0006753335844687604</v>
       </c>
       <c r="EN10" t="n">
         <v>-0</v>
@@ -5986,16 +5986,16 @@
         <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.04687477570126973</v>
+        <v>0.0008363166363169267</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.01847597564686349</v>
+        <v>-0.002505253993154952</v>
       </c>
       <c r="ET10" t="n">
         <v>-0</v>
@@ -6004,16 +6004,16 @@
         <v>-0</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.03681747963006655</v>
+        <v>0.002447395909923932</v>
       </c>
       <c r="EW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.03042504632219524</v>
+        <v>-0.005547332671150434</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
@@ -6022,7 +6022,7 @@
         <v>-0</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.0001037867407597082</v>
+        <v>0.001025703622407463</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
@@ -6031,16 +6031,16 @@
         <v>-0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.002845819723679651</v>
+        <v>0.002605065605073023</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.00067723714922764</v>
+        <v>-0.0002762269598316975</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
@@ -6049,16 +6049,16 @@
         <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.03170386045000795</v>
+        <v>0.007204136191809409</v>
       </c>
       <c r="FL10" t="n">
         <v>0</v>
       </c>
       <c r="FM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0.03186899088181164</v>
+        <v>-0.002968709056187627</v>
       </c>
       <c r="FO10" t="n">
         <v>-0</v>
@@ -6067,7 +6067,7 @@
         <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.0004423759510849711</v>
+        <v>-0.0009865918755318052</v>
       </c>
       <c r="FR10" t="n">
         <v>-0</v>
@@ -6076,28 +6076,28 @@
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.006737069897284935</v>
+        <v>0.001974036341671114</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0.04845294949849172</v>
+        <v>0.002216685048000268</v>
       </c>
       <c r="FX10" t="n">
         <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.07956879762677511</v>
+        <v>-0.005499386375245662</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
         <v>-0</v>
@@ -6112,27 +6112,27 @@
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>-0.04261807501368523</v>
+        <v>-0.0006049232994437387</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0.1357483605627878</v>
+        <v>-0.0488525405605276</v>
       </c>
       <c r="B11" t="n">
-        <v>0.471545222356621</v>
+        <v>0.05741552958391704</v>
       </c>
       <c r="C11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1184000133006523</v>
+        <v>-0.004322573270932714</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -6147,22 +6147,22 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1095341113517893</v>
+        <v>-0.04311277864094578</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3509239546148908</v>
+        <v>0.08505339781865738</v>
       </c>
       <c r="L11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2201235638612972</v>
+        <v>-0.004903720824678048</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P11" t="n">
         <v>-0</v>
@@ -6174,64 +6174,64 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01782538569656915</v>
+        <v>0.01077453653424605</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2808156362737016</v>
+        <v>0.01100519878970546</v>
       </c>
       <c r="U11" t="n">
         <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0319595922127156</v>
+        <v>0.003743358954043791</v>
       </c>
       <c r="X11" t="n">
         <v>-0</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.289197998188628e-11</v>
+        <v>-5.600659570097043e-12</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.04006459550416364</v>
+        <v>0.002631542412140384</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.01019858267952406</v>
+        <v>-0.006233789276640673</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>-0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0.06171588043171918</v>
+        <v>-0.00513155518801875</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.2291948306416728</v>
+        <v>0.02763008075276526</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
@@ -6240,52 +6240,52 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.07473025865300924</v>
+        <v>-0.008840006300955178</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS11" t="n">
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.1003439603704824</v>
+        <v>-0.01733698413437168</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.5676199226800873</v>
+        <v>0.07149748565518385</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.187371086190169</v>
+        <v>-0.02523161957208988</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA11" t="n">
         <v>-0</v>
       </c>
       <c r="BB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>-0.0892895521631611</v>
+        <v>-0.04048774741432623</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.02484930725929589</v>
+        <v>0.01265733878992723</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,13 +6294,13 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.3197824502166963</v>
+        <v>-0.01766180280746327</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
         <v>0</v>
@@ -6309,10 +6309,10 @@
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0.03689702504336245</v>
+        <v>0.009031189737577935</v>
       </c>
       <c r="BM11" t="n">
-        <v>-0.02966004789015406</v>
+        <v>0.02497182681622997</v>
       </c>
       <c r="BN11" t="n">
         <v>-0</v>
@@ -6321,13 +6321,13 @@
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.0486838642217382</v>
+        <v>0.03142422371031091</v>
       </c>
       <c r="BQ11" t="n">
         <v>-0</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
@@ -6336,22 +6336,22 @@
         <v>-0</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.07345566494832846</v>
+        <v>0.00323166169918674</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.4399428602972525</v>
+        <v>0.06069252227420747</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.01284693057299236</v>
+        <v>-0.003797701314797548</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
@@ -6363,46 +6363,46 @@
         <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.03846645660931336</v>
+        <v>0.0240460692253205</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.1205331213713673</v>
+        <v>-0.02836369225641616</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.004452210365959581</v>
+        <v>-0.005481789585934684</v>
       </c>
       <c r="CI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL11" t="n">
         <v>-0</v>
       </c>
       <c r="CM11" t="n">
-        <v>-0.1032579009833072</v>
+        <v>0.002882167016464611</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.0147022360568047</v>
+        <v>-0.03720620553387993</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.07180381608456735</v>
+        <v>0.006448504368644759</v>
       </c>
       <c r="CR11" t="n">
         <v>-0</v>
@@ -6414,22 +6414,22 @@
         <v>-0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.0158223023761332</v>
+        <v>0.02189377800083469</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.1210588422898496</v>
+        <v>-0.02828303016338695</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.01175359600926998</v>
+        <v>-0.01032678732536187</v>
       </c>
       <c r="DA11" t="n">
         <v>0</v>
@@ -6438,112 +6438,112 @@
         <v>0</v>
       </c>
       <c r="DC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD11" t="n">
         <v>0</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.05663395425012152</v>
+        <v>0.01932697422255089</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.2237433202717032</v>
+        <v>-0.04356228359397669</v>
       </c>
       <c r="DG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH11" t="n">
         <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.08276643242128741</v>
+        <v>-0.0251115608964448</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN11" t="n">
-        <v>-0.06310804839520744</v>
+        <v>-0.009288317736758948</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.06499354676030347</v>
+        <v>-0.02053560333037056</v>
       </c>
       <c r="DP11" t="n">
         <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.02238770425467532</v>
+        <v>0.002399613086582503</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW11" t="n">
-        <v>-0.007604919893029321</v>
+        <v>0.01089283118136094</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.1088560744310052</v>
+        <v>0.02016895799054737</v>
       </c>
       <c r="DY11" t="n">
         <v>0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.09295560656471952</v>
+        <v>0.01047642981715336</v>
       </c>
       <c r="EB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC11" t="n">
         <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>-0.0280664515375161</v>
+        <v>0.01668922564065249</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.01490592077984777</v>
+        <v>-0.004857055780910359</v>
       </c>
       <c r="EH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.0008176124074175709</v>
+        <v>-0.01533739040072436</v>
       </c>
       <c r="EK11" t="n">
         <v>-0</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
         <v>-0</v>
@@ -6552,19 +6552,19 @@
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.01199850614588686</v>
+        <v>0.01249296003110801</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.09958723909169671</v>
+        <v>-0.01249079962615636</v>
       </c>
       <c r="EQ11" t="n">
         <v>0</v>
       </c>
       <c r="ER11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.00327027413583223</v>
+        <v>-0.01329036303113838</v>
       </c>
       <c r="ET11" t="n">
         <v>-0</v>
@@ -6573,43 +6573,43 @@
         <v>-0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.0164381362783753</v>
+        <v>0.02611435662741643</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.1307353684155892</v>
+        <v>-0.03566842577410072</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.04560414542526635</v>
+        <v>-0.00947597176587868</v>
       </c>
       <c r="FC11" t="n">
         <v>-0</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>-0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.03462099277012803</v>
+        <v>0.01422725189349505</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.07653719183352026</v>
+        <v>-0.0124215915156757</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
@@ -6618,7 +6618,7 @@
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.1068797934129631</v>
+        <v>0.004049732262889075</v>
       </c>
       <c r="FL11" t="n">
         <v>0</v>
@@ -6630,40 +6630,40 @@
         <v>-0</v>
       </c>
       <c r="FO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP11" t="n">
-        <v>-0.03968380987151685</v>
+        <v>-0.007505123370199098</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.039867938709974</v>
+        <v>0.005115006844550455</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.008234770943463005</v>
+        <v>0.008038988047609889</v>
       </c>
       <c r="FU11" t="n">
         <v>-0</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
         <v>-0</v>
       </c>
       <c r="FX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0.1101802597512309</v>
+        <v>0.007668252421368283</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.02819735980326554</v>
+        <v>-0.01965718509073619</v>
       </c>
       <c r="GA11" t="n">
         <v>-0</v>
@@ -6672,19 +6672,19 @@
         <v>-0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF11" t="n">
         <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,25 +6692,25 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4098900443988437</v>
+        <v>0.003246145938088831</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.08227799030695876</v>
+        <v>-0.001527200389261162</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1604722546308923</v>
+        <v>-0.001158502601778101</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -6719,22 +6719,22 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2794223289197117</v>
+        <v>0.004624020951653088</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1138799556426775</v>
+        <v>-0.001720084787927141</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1423336817695231</v>
+        <v>-0.001690238771849059</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -6746,88 +6746,88 @@
         <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1524079558346236</v>
+        <v>0.0006969453066275674</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1057144407090385</v>
+        <v>-0.0009549024949279734</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.03065315048680929</v>
+        <v>-0.0001415100911127328</v>
       </c>
       <c r="Z12" t="n">
         <v>-0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB12" t="n">
         <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.04597981453520556</v>
+        <v>4.404200376691617e-06</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.00278627200385047</v>
+        <v>-0.0001020335567861844</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-1.300750975096672e-12</v>
+        <v>1.840167941120933e-14</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.09490530666588119</v>
+        <v>0.001604726381523135</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.03287361078802519</v>
+        <v>0.0004323485535315282</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.0752632521930586</v>
+        <v>-0.0004133193889441389</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT12" t="n">
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.5262943068288627</v>
+        <v>0.005942893083874314</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
@@ -6836,25 +6836,25 @@
         <v>-0</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.08213783715734063</v>
+        <v>-0.0004149777765591395</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0.1029033420601003</v>
+        <v>-0.0006170956639976648</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC12" t="n">
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.07224892749850209</v>
+        <v>-0.001841515466882667</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -6863,13 +6863,13 @@
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1566819335878966</v>
+        <v>-0.001411455808358268</v>
       </c>
       <c r="BH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>-0.08862330491796601</v>
+        <v>-0.0001788603181808363</v>
       </c>
       <c r="BJ12" t="n">
         <v>0</v>
@@ -6878,10 +6878,10 @@
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.01903338426589549</v>
+        <v>0.0004278732613613894</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
@@ -6890,13 +6890,13 @@
         <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.09855255477021753</v>
+        <v>0.003131629111873912</v>
       </c>
       <c r="BQ12" t="n">
         <v>-0</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.06142185439939696</v>
+        <v>0.0003713864175881696</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
@@ -6908,34 +6908,34 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.2440550821483009</v>
+        <v>0.004189769808260179</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.0001067524158789265</v>
+        <v>-0.0008543034022637125</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA12" t="n">
-        <v>-0.04890422322457139</v>
+        <v>-0.0004146378677923059</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
         <v>0</v>
       </c>
       <c r="CD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.1180164843711058</v>
+        <v>-0.001653726510168594</v>
       </c>
       <c r="CF12" t="n">
         <v>0</v>
@@ -6944,13 +6944,13 @@
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.0002147394170136029</v>
+        <v>0.0007636445395584998</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.05404896621148526</v>
+        <v>0.0002087748291688786</v>
       </c>
       <c r="CK12" t="n">
         <v>-0</v>
@@ -6959,10 +6959,10 @@
         <v>-0</v>
       </c>
       <c r="CM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.05571621167399746</v>
+        <v>-0.001462240595665281</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
@@ -6971,13 +6971,13 @@
         <v>-0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.06379555282570942</v>
+        <v>0.0001787981318005017</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.009798578260283432</v>
+        <v>-0.0005871936154300452</v>
       </c>
       <c r="CT12" t="n">
         <v>-0</v>
@@ -6986,10 +6986,10 @@
         <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.1106735706611887</v>
+        <v>-0.001773862903330104</v>
       </c>
       <c r="CX12" t="n">
         <v>-0</v>
@@ -6998,13 +6998,13 @@
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.004626446785627507</v>
+        <v>0.0005327749870042511</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.05954125072354864</v>
+        <v>0.0005128328706557613</v>
       </c>
       <c r="DC12" t="n">
         <v>0</v>
@@ -7016,7 +7016,7 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.2577705968754488</v>
+        <v>-0.0008134443995798789</v>
       </c>
       <c r="DG12" t="n">
         <v>-0</v>
@@ -7025,52 +7025,52 @@
         <v>-0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.05676800317147357</v>
+        <v>-0.0006387282976606317</v>
       </c>
       <c r="DJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0.04572640180826062</v>
+        <v>-0.0005509655906947051</v>
       </c>
       <c r="DL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.0186753328669094</v>
+        <v>-0.0005558317232563456</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.01057363926653227</v>
+        <v>0.0002223652360671881</v>
       </c>
       <c r="DS12" t="n">
         <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.01706972545431486</v>
+        <v>0.0005083824635174211</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
         <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.08513952644225262</v>
+        <v>0.001235515983783688</v>
       </c>
       <c r="DY12" t="n">
         <v>0</v>
@@ -7079,13 +7079,13 @@
         <v>-0</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.04212632996419635</v>
+        <v>-0.0007586093475600698</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.007186996227142493</v>
+        <v>0.0001573696483515261</v>
       </c>
       <c r="ED12" t="n">
         <v>0</v>
@@ -7094,25 +7094,25 @@
         <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.04469998879471928</v>
+        <v>-0.001058619275289009</v>
       </c>
       <c r="EH12" t="n">
         <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.03184625342459373</v>
+        <v>0.0004683860430682178</v>
       </c>
       <c r="EK12" t="n">
         <v>-0</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.04868115966043891</v>
+        <v>-0.0002370635914775763</v>
       </c>
       <c r="EM12" t="n">
         <v>-0</v>
@@ -7124,22 +7124,22 @@
         <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.07096211506215327</v>
+        <v>-0.001164700987408045</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
         <v>-0</v>
       </c>
       <c r="ES12" t="n">
-        <v>-0.02246581162229058</v>
+        <v>-0.0003289322881345127</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0.02248952459950865</v>
+        <v>-0.0002314257668706953</v>
       </c>
       <c r="EV12" t="n">
         <v>-0</v>
@@ -7148,10 +7148,10 @@
         <v>-0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.1151516076051104</v>
+        <v>-0.001958588011594377</v>
       </c>
       <c r="EZ12" t="n">
         <v>0</v>
@@ -7160,13 +7160,13 @@
         <v>-0</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.02033570527087088</v>
+        <v>0.0003676609312450939</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.06151894651262665</v>
+        <v>0.0002346836571444418</v>
       </c>
       <c r="FE12" t="n">
         <v>-0</v>
@@ -7175,37 +7175,37 @@
         <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.08161482493172421</v>
+        <v>-0.0004561763322339462</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.06190685197872927</v>
+        <v>0.0003672679324081981</v>
       </c>
       <c r="FL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.03084676356172001</v>
+        <v>7.4581032514135e-05</v>
       </c>
       <c r="FN12" t="n">
         <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.01597373766650189</v>
+        <v>-7.236693279895649e-05</v>
       </c>
       <c r="FR12" t="n">
         <v>-0</v>
@@ -7214,28 +7214,28 @@
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.007080682751813538</v>
+        <v>0.0002781047125355201</v>
       </c>
       <c r="FU12" t="n">
         <v>-0</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.05367644865522656</v>
+        <v>0.0004845635353959671</v>
       </c>
       <c r="FW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX12" t="n">
         <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.07605121471279719</v>
+        <v>-0.001528225738202969</v>
       </c>
       <c r="GA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB12" t="n">
         <v>-0</v>
@@ -7244,16 +7244,16 @@
         <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
-        <v>-0.09427837772574504</v>
+        <v>0.0007248185530438483</v>
       </c>
       <c r="GF12" t="n">
         <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,7 +7261,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5957070299934158</v>
+        <v>1.185217597296268</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -7270,7 +7270,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1696867093349326</v>
+        <v>-0.5087076615946142</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -7282,13 +7282,13 @@
         <v>-0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2339278100894732</v>
+        <v>-0.125063679014855</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.448974670023354</v>
+        <v>1.482964424584295</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2058805598437507</v>
+        <v>-0.5765215076393559</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -7306,106 +7306,106 @@
         <v>-0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.2173415236387826</v>
+        <v>-0.08809681896325477</v>
       </c>
       <c r="S13" t="n">
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2123233266226793</v>
+        <v>0.2951793319845037</v>
       </c>
       <c r="U13" t="n">
         <v>-0</v>
       </c>
       <c r="V13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.00385825139451771</v>
+        <v>-0.2057084370601451</v>
       </c>
       <c r="X13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z13" t="n">
         <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.04436097778096185</v>
+        <v>-0.2971439742375101</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.05839711786124133</v>
+        <v>0.0370682782749094</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.01209987869598493</v>
+        <v>-0.08924349905081934</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0.005791483618786395</v>
+        <v>0.01813520234109972</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.134595462251407</v>
+        <v>0.647218271977446</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.002605866371041171</v>
+        <v>0.3151340337522126</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
       </c>
       <c r="AS13" t="n">
-        <v>-0.04072840051334569</v>
+        <v>-0.01990357901397147</v>
       </c>
       <c r="AT13" t="n">
         <v>-0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.6524579953298536</v>
+        <v>1.906082763680571</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.06351245641272907</v>
+        <v>-0.3466726432555277</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
@@ -7414,16 +7414,16 @@
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>-0.1647765097551635</v>
+        <v>0.05734532317016303</v>
       </c>
       <c r="BC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.1373202862337907</v>
+        <v>-0.4187780066644352</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,25 +7432,25 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.2926253679172579</v>
+        <v>-0.4664721796651017</v>
       </c>
       <c r="BH13" t="n">
         <v>0</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
         <v>0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0.1399409036545141</v>
+        <v>-0.06902629970221594</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>-0.03139032031344098</v>
+        <v>0.1100041437924637</v>
       </c>
       <c r="BN13" t="n">
         <v>-0</v>
@@ -7459,25 +7459,25 @@
         <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.2181287444900121</v>
+        <v>0.2565249993184942</v>
       </c>
       <c r="BQ13" t="n">
         <v>-0</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0.005477750310742354</v>
+        <v>0.1790245898771092</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.4078918779930873</v>
+        <v>1.316920678674573</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
@@ -7486,25 +7486,25 @@
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.04297685847085359</v>
+        <v>-0.2710160758287363</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
-        <v>-0.05803283620738584</v>
+        <v>-0.2159210613528768</v>
       </c>
       <c r="CD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.1662124194299424</v>
+        <v>-0.6714875314215168</v>
       </c>
       <c r="CF13" t="n">
         <v>-0</v>
@@ -7513,34 +7513,34 @@
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.003134508757096788</v>
+        <v>0.1400475975698884</v>
       </c>
       <c r="CI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>-0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.0994535199869427</v>
+        <v>0.07077091264935598</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.1079344122890634</v>
+        <v>-0.586243147508054</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
         <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.06457839891453634</v>
+        <v>0.1040190846400225</v>
       </c>
       <c r="CR13" t="n">
         <v>-0</v>
@@ -7552,40 +7552,40 @@
         <v>-0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.01189848822070122</v>
+        <v>0.01263317585704447</v>
       </c>
       <c r="CV13" t="n">
         <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.1435100062129844</v>
+        <v>-0.6460743325784353</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.002914210024429154</v>
+        <v>0.09994976969990746</v>
       </c>
       <c r="DA13" t="n">
         <v>0</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.08346824965068411</v>
+        <v>0.1365030123987227</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.2757533220253617</v>
+        <v>-0.2650128418010136</v>
       </c>
       <c r="DG13" t="n">
         <v>-0</v>
@@ -7594,7 +7594,7 @@
         <v>-0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.03742216675639115</v>
+        <v>0.001188408820893325</v>
       </c>
       <c r="DJ13" t="n">
         <v>-0</v>
@@ -7603,25 +7603,25 @@
         <v>0</v>
       </c>
       <c r="DL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.03382726213238105</v>
+        <v>-0.1527310611334255</v>
       </c>
       <c r="DN13" t="n">
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.0524889167509658</v>
+        <v>-0.282372928175631</v>
       </c>
       <c r="DP13" t="n">
         <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.01897198861855883</v>
+        <v>0.02527764099881244</v>
       </c>
       <c r="DS13" t="n">
         <v>-0</v>
@@ -7630,43 +7630,43 @@
         <v>0</v>
       </c>
       <c r="DU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>-0.02259084022748285</v>
+        <v>-0.2682034397995977</v>
       </c>
       <c r="DW13" t="n">
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.1287055737378587</v>
+        <v>0.4311930797098074</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.04856352747623631</v>
+        <v>-0.2688737073820104</v>
       </c>
       <c r="EB13" t="n">
         <v>-0</v>
       </c>
       <c r="EC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>-0.002166771162325189</v>
+        <v>0.2437364332092798</v>
       </c>
       <c r="EF13" t="n">
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.03605802408271335</v>
+        <v>-0.2927423262201128</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
@@ -7675,52 +7675,52 @@
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.03003494941585363</v>
+        <v>-0.04079657010266549</v>
       </c>
       <c r="EK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.137731513553764</v>
+        <v>0.05303673578530386</v>
       </c>
       <c r="EO13" t="n">
         <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.1294142052476756</v>
+        <v>-0.4327857021338016</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.01001814084406722</v>
+        <v>-0.01332497492532339</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU13" t="n">
         <v>0</v>
       </c>
       <c r="EV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.04018003600841379</v>
+        <v>0.1350836462168304</v>
       </c>
       <c r="EX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.1730053009386717</v>
+        <v>-0.7478174870713271</v>
       </c>
       <c r="EZ13" t="n">
         <v>-0</v>
@@ -7729,25 +7729,25 @@
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.006680594824809261</v>
+        <v>0.08283698895017998</v>
       </c>
       <c r="FC13" t="n">
         <v>-0</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>-0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.08106363987243112</v>
+        <v>0.1358316440088084</v>
       </c>
       <c r="FG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.09365301958237854</v>
+        <v>-0.2786981191275719</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
@@ -7756,25 +7756,25 @@
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.07364333820539103</v>
+        <v>-0.06168781112966576</v>
       </c>
       <c r="FL13" t="n">
         <v>0</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
         <v>0</v>
       </c>
       <c r="FO13" t="n">
-        <v>-0.08289972846443332</v>
+        <v>-0.2170243165505544</v>
       </c>
       <c r="FP13" t="n">
         <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.02461631250917898</v>
+        <v>-0.06394074838965132</v>
       </c>
       <c r="FR13" t="n">
         <v>-0</v>
@@ -7783,46 +7783,46 @@
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.005662067530327327</v>
+        <v>0.05679715598349662</v>
       </c>
       <c r="FU13" t="n">
         <v>-0</v>
       </c>
       <c r="FV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW13" t="n">
         <v>-0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.02765675302878911</v>
+        <v>-0.2717723594668973</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.1405516112716614</v>
+        <v>-0.3220315751040938</v>
       </c>
       <c r="GA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC13" t="n">
         <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0.02207852803345344</v>
+        <v>0.1561356267870529</v>
       </c>
     </row>
     <row r="14">
@@ -8396,19 +8396,19 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.5856001959820877</v>
+        <v>-0.6478942283082595</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5022069967477493</v>
+        <v>0.2914116423392542</v>
       </c>
       <c r="D15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2019405168929685</v>
+        <v>0.3573365100021121</v>
       </c>
       <c r="F15" t="n">
         <v>-0</v>
@@ -8426,25 +8426,25 @@
         <v>-0</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4466406107400447</v>
+        <v>-0.8491449388215113</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3649670802807409</v>
+        <v>0.2614971367250337</v>
       </c>
       <c r="M15" t="n">
         <v>-0</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3209053489582296</v>
+        <v>0.2832491774173554</v>
       </c>
       <c r="O15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R15" t="n">
         <v>-0</v>
@@ -8453,16 +8453,16 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1810590841102909</v>
+        <v>-0.2040824869085449</v>
       </c>
       <c r="U15" t="n">
-        <v>0.01800573941513638</v>
+        <v>-0.1381991078588617</v>
       </c>
       <c r="V15" t="n">
         <v>-0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.03597234547544773</v>
+        <v>-0.0828647371651253</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -8471,52 +8471,52 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB15" t="n">
         <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.08992670870348285</v>
+        <v>-0.0306019591384103</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.001589339339085907</v>
+        <v>0.1015001184864049</v>
       </c>
       <c r="AE15" t="n">
         <v>-0</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.02538595015608277</v>
+        <v>0.03204285376171379</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
         <v>-0</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.3067323077130655</v>
+        <v>-0.3807231062937763</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.0530606601333064</v>
+        <v>0.04619011503155655</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.02159134968205524</v>
+        <v>-0.3623431556318693</v>
       </c>
       <c r="AP15" t="n">
         <v>-0</v>
@@ -8525,7 +8525,7 @@
         <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
         <v>-0</v>
@@ -8534,46 +8534,46 @@
         <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>-0.617233362100586</v>
+        <v>-1.009051285480639</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.3770445913161772</v>
+        <v>-0.02373168421458201</v>
       </c>
       <c r="AW15" t="n">
         <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.0224074979188193</v>
+        <v>-0.06240384275433162</v>
       </c>
       <c r="AY15" t="n">
         <v>-0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC15" t="n">
         <v>-0</v>
       </c>
       <c r="BD15" t="n">
-        <v>-0.1065925556001996</v>
+        <v>0.4377223722174859</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.1608053621663371</v>
+        <v>0.2902703894315217</v>
       </c>
       <c r="BF15" t="n">
         <v>-0</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.4640094995812941</v>
+        <v>0.6512330149958828</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI15" t="n">
         <v>0</v>
@@ -8588,25 +8588,25 @@
         <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>-0.1452236846289819</v>
+        <v>0.02056988638582829</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.09469487937371532</v>
+        <v>-0.02460740961295904</v>
       </c>
       <c r="BO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP15" t="n">
-        <v>-0.06245659527023845</v>
+        <v>-0.03891897386786528</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT15" t="n">
         <v>0</v>
@@ -8615,16 +8615,16 @@
         <v>0</v>
       </c>
       <c r="BV15" t="n">
-        <v>-0.2765555048289</v>
+        <v>-0.6579446257966903</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.4013442095394716</v>
+        <v>-0.03467811699314138</v>
       </c>
       <c r="BX15" t="n">
         <v>-0</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.004434337996179909</v>
+        <v>-0.04505153753157709</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -8636,31 +8636,31 @@
         <v>-0</v>
       </c>
       <c r="CC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.1432574306917467</v>
+        <v>0.379892055062188</v>
       </c>
       <c r="CF15" t="n">
-        <v>-0.05865092973877033</v>
+        <v>-0.1025571504782499</v>
       </c>
       <c r="CG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.07377024584961395</v>
+        <v>-0.09181980681504485</v>
       </c>
       <c r="CI15" t="n">
         <v>0</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL15" t="n">
         <v>0</v>
@@ -8669,16 +8669,16 @@
         <v>-0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.04580832386164815</v>
+        <v>0.3089989689802744</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.009052390728214236</v>
+        <v>-0.03721175094642184</v>
       </c>
       <c r="CP15" t="n">
         <v>0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.1053647506541834</v>
+        <v>-0.1518825861966959</v>
       </c>
       <c r="CR15" t="n">
         <v>0</v>
@@ -8696,16 +8696,16 @@
         <v>-0</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.08292950891231435</v>
+        <v>0.349247143794073</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0.05278747009344598</v>
+        <v>-0.08115513609193273</v>
       </c>
       <c r="CY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-0.03297007351594661</v>
+        <v>-0.06810017084170526</v>
       </c>
       <c r="DA15" t="n">
         <v>-0</v>
@@ -8714,7 +8714,7 @@
         <v>-0</v>
       </c>
       <c r="DC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD15" t="n">
         <v>-0</v>
@@ -8723,16 +8723,16 @@
         <v>-0</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.1128864293612076</v>
+        <v>0.04984562520329686</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.0698839246658456</v>
+        <v>0.03348037149164617</v>
       </c>
       <c r="DH15" t="n">
         <v>0</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.09902490285184505</v>
+        <v>0.02583563876850147</v>
       </c>
       <c r="DJ15" t="n">
         <v>0</v>
@@ -8744,52 +8744,52 @@
         <v>-0</v>
       </c>
       <c r="DM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.0009514928174906399</v>
+        <v>0.159293761961485</v>
       </c>
       <c r="DP15" t="n">
-        <v>-0.04621032599136168</v>
+        <v>-0.06185794293549377</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.1014787998134182</v>
+        <v>-0.06252070506743891</v>
       </c>
       <c r="DS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV15" t="n">
         <v>-0</v>
       </c>
       <c r="DW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.0147438247669354</v>
+        <v>-0.2443349539639854</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.1214368583341717</v>
+        <v>-0.03389683314347385</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.09464167323103202</v>
+        <v>0.2116493629259438</v>
       </c>
       <c r="EB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC15" t="n">
         <v>-0</v>
@@ -8801,46 +8801,46 @@
         <v>0</v>
       </c>
       <c r="EF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.04739073703616527</v>
+        <v>0.2165696301693601</v>
       </c>
       <c r="EH15" t="n">
-        <v>-0.03314198676337968</v>
+        <v>0.09452352555514176</v>
       </c>
       <c r="EI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>-0.1130302533890585</v>
+        <v>-0.07416220991878822</v>
       </c>
       <c r="EK15" t="n">
         <v>0</v>
       </c>
       <c r="EL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM15" t="n">
         <v>0</v>
       </c>
       <c r="EN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO15" t="n">
         <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.02784314165513375</v>
+        <v>0.2551823004371448</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.09325877213996679</v>
+        <v>0.07383431355915128</v>
       </c>
       <c r="ER15" t="n">
         <v>0</v>
       </c>
       <c r="ES15" t="n">
-        <v>-0.04580871629295503</v>
+        <v>-0.01117261186294968</v>
       </c>
       <c r="ET15" t="n">
         <v>0</v>
@@ -8849,34 +8849,34 @@
         <v>0</v>
       </c>
       <c r="EV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.09084816304900233</v>
+        <v>0.419585384286311</v>
       </c>
       <c r="EZ15" t="n">
-        <v>-0.04808789099140418</v>
+        <v>-0.08824167977884338</v>
       </c>
       <c r="FA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB15" t="n">
-        <v>-0.05293122716942122</v>
+        <v>-0.09549401757295148</v>
       </c>
       <c r="FC15" t="n">
         <v>0</v>
       </c>
       <c r="FD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF15" t="n">
         <v>0</v>
@@ -8885,70 +8885,70 @@
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.1511096807473324</v>
+        <v>0.08501947467815164</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.1640419176618498</v>
+        <v>0.2445605977325841</v>
       </c>
       <c r="FJ15" t="n">
         <v>0</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.2202719246022012</v>
+        <v>0.2305485915617206</v>
       </c>
       <c r="FL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP15" t="n">
         <v>0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.000122649232929846</v>
+        <v>0.001557106707699393</v>
       </c>
       <c r="FR15" t="n">
-        <v>-0.06476043956903237</v>
+        <v>-0.005335269013560164</v>
       </c>
       <c r="FS15" t="n">
         <v>0</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.01150767731223456</v>
+        <v>-0.02131421605597281</v>
       </c>
       <c r="FU15" t="n">
         <v>0</v>
       </c>
       <c r="FV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY15" t="n">
         <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>-0.09324930545369339</v>
+        <v>0.1887370741972324</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0.03898125574773053</v>
+        <v>0.2030959035761905</v>
       </c>
       <c r="GB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD15" t="n">
         <v>0</v>
@@ -8957,7 +8957,7 @@
         <v>0</v>
       </c>
       <c r="GF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG15" t="n">
         <v>-0</v>
@@ -8968,7 +8968,7 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1719540176490533</v>
+        <v>0.3100159468294384</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -8977,10 +8977,10 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.05510748947682456</v>
+        <v>0.06811120432950202</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.08715665807871681</v>
+        <v>-0.1611041023914769</v>
       </c>
       <c r="G16" t="n">
         <v>-0</v>
@@ -8992,10 +8992,10 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1390656461686944</v>
+        <v>0.3933133250076254</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -9004,16 +9004,16 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.02624024872693008</v>
+        <v>-0.05829223161404149</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.07232889606455117</v>
+        <v>-0.1864319653107201</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -9022,49 +9022,49 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.02727864124550647</v>
+        <v>0.1339420394090474</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.01982417378577795</v>
+        <v>-0.04676546405744341</v>
       </c>
       <c r="X16" t="n">
-        <v>0.00177633182022937</v>
+        <v>-0.0005520063346231733</v>
       </c>
       <c r="Y16" t="n">
         <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.003768989232316697</v>
+        <v>-0.01381869985767347</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.00501737195938803</v>
+        <v>-0.06484855263153887</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.002169836679830884</v>
+        <v>0.01799787771950286</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>-0</v>
@@ -9076,34 +9076,34 @@
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.02590748447132112</v>
+        <v>0.08563412067092957</v>
       </c>
       <c r="AM16" t="n">
         <v>-0</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.0008909777968175589</v>
+        <v>-0.03916690223177431</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.04164852344248137</v>
+        <v>-0.04927568746796703</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR16" t="n">
         <v>-0</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.1271298540695137</v>
+        <v>0.582070555182156</v>
       </c>
       <c r="AV16" t="n">
         <v>-0</v>
@@ -9112,25 +9112,25 @@
         <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>-0.03770247805047881</v>
+        <v>-0.2317705639356958</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0.09526868018307566</v>
+        <v>-0.2360066015405801</v>
       </c>
       <c r="AZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
         <v>-0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC16" t="n">
         <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.03604310439482949</v>
+        <v>-0.1412913627122537</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
@@ -9139,106 +9139,106 @@
         <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.03919740946567946</v>
+        <v>0.01172857157645602</v>
       </c>
       <c r="BH16" t="n">
-        <v>-0.02183761878672415</v>
+        <v>-0.06330069356572139</v>
       </c>
       <c r="BI16" t="n">
         <v>-0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
         <v>0</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.03191466590888783</v>
+        <v>0.1317949683534462</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO16" t="n">
         <v>-0</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.003310019553334726</v>
+        <v>0.07966873889276965</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.008157693347078132</v>
+        <v>0.02499458703803637</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
         <v>0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
         <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.07007692543435005</v>
+        <v>0.311414107391049</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX16" t="n">
         <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>-0.02844187206118379</v>
+        <v>-0.05773175388937433</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0.02748117557111489</v>
+        <v>-0.09267839471568112</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
       </c>
       <c r="CB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD16" t="n">
         <v>0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.03525370561808943</v>
+        <v>-0.1264526959990391</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG16" t="n">
         <v>-0</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.0008299013390268792</v>
+        <v>0.01543443378994865</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.02571409301663053</v>
+        <v>0.04786293207660536</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
         <v>0</v>
       </c>
       <c r="CL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM16" t="n">
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.003508196526299338</v>
+        <v>-0.1484235205822863</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
@@ -9247,37 +9247,37 @@
         <v>-0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.003662989812347138</v>
+        <v>0.1087592152210064</v>
       </c>
       <c r="CR16" t="n">
-        <v>-0.02252779228620241</v>
+        <v>0.03336387973319571</v>
       </c>
       <c r="CS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV16" t="n">
         <v>-0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.03222189101000417</v>
+        <v>-0.1203053099527209</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
         <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.002035440516834429</v>
+        <v>-0.009253540863334591</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.03141525101889747</v>
+        <v>0.08180846623758554</v>
       </c>
       <c r="DB16" t="n">
         <v>0</v>
@@ -9286,40 +9286,40 @@
         <v>-0</v>
       </c>
       <c r="DD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.02464504027803544</v>
+        <v>-0.1166518942729981</v>
       </c>
       <c r="DG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.04390092452442424</v>
+        <v>-0.1717712997393305</v>
       </c>
       <c r="DJ16" t="n">
-        <v>-0.000415718521753898</v>
+        <v>0.05067825537158664</v>
       </c>
       <c r="DK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.0112438305052271</v>
+        <v>-0.06995829549528715</v>
       </c>
       <c r="DP16" t="n">
         <v>0</v>
@@ -9328,37 +9328,37 @@
         <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.01783998545642576</v>
+        <v>0.01555041194180345</v>
       </c>
       <c r="DS16" t="n">
-        <v>-1.520451815036939e-05</v>
+        <v>0.07062148928896106</v>
       </c>
       <c r="DT16" t="n">
         <v>-0</v>
       </c>
       <c r="DU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV16" t="n">
         <v>0</v>
       </c>
       <c r="DW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.02362827017215603</v>
+        <v>-0.1114566189214003</v>
       </c>
       <c r="DY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ16" t="n">
         <v>-0</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.006528698083716571</v>
+        <v>0.009111141093780377</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.012803167295742</v>
+        <v>0.02823263846278938</v>
       </c>
       <c r="EC16" t="n">
         <v>0</v>
@@ -9367,25 +9367,25 @@
         <v>0</v>
       </c>
       <c r="EE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF16" t="n">
         <v>0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.03508480927577015</v>
+        <v>-0.0354489578088179</v>
       </c>
       <c r="EH16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI16" t="n">
         <v>-0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.01182183706424115</v>
+        <v>-0.03623872431755571</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.03338423356741664</v>
+        <v>-0.03767154240204373</v>
       </c>
       <c r="EL16" t="n">
         <v>-0</v>
@@ -9400,22 +9400,22 @@
         <v>0</v>
       </c>
       <c r="EP16" t="n">
-        <v>-0.0211354864433247</v>
+        <v>-0.0130880037112671</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
         <v>-0</v>
       </c>
       <c r="ES16" t="n">
-        <v>-0.007802926414176778</v>
+        <v>-0.08802217275359603</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.006600795818346028</v>
+        <v>-0.01793812027157698</v>
       </c>
       <c r="EU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV16" t="n">
         <v>0</v>
@@ -9427,46 +9427,46 @@
         <v>0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.02995722307648519</v>
+        <v>-0.1512773396245544</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA16" t="n">
         <v>-0</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.002203834215592546</v>
+        <v>-0.0127472065120183</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.02706645431695889</v>
+        <v>0.0604761911094209</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.001231492219864073</v>
+        <v>0.09690481661052079</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ16" t="n">
         <v>-0</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.009410707390329997</v>
+        <v>-0.02623287152169475</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.02954821090179123</v>
+        <v>0.1271336068629508</v>
       </c>
       <c r="FM16" t="n">
         <v>0</v>
@@ -9478,10 +9478,10 @@
         <v>0</v>
       </c>
       <c r="FP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>-0.001983613360450768</v>
+        <v>-0.02284104427554435</v>
       </c>
       <c r="FR16" t="n">
         <v>-0</v>
@@ -9490,43 +9490,43 @@
         <v>-0</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.01128133942941411</v>
+        <v>0.06178755696227989</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.01844022066727466</v>
+        <v>-0.09293733920215562</v>
       </c>
       <c r="FV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.005415781100468099</v>
+        <v>-0.04592804335817525</v>
       </c>
       <c r="GA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB16" t="n">
         <v>0</v>
       </c>
       <c r="GC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0.02005812897815362</v>
+        <v>0.08713129147864047</v>
       </c>
       <c r="GE16" t="n">
         <v>-0</v>
       </c>
       <c r="GF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG16" t="n">
         <v>-0</v>
@@ -9537,7 +9537,7 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1057968697325088</v>
+        <v>0.169065790212127</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -9546,37 +9546,37 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.08475484688763088</v>
+        <v>-0.05066034267543727</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.02057865388933401</v>
+        <v>-0.0492492105172555</v>
       </c>
       <c r="G17" t="n">
         <v>-0</v>
       </c>
       <c r="H17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.07480445114314249</v>
+        <v>0.1865473395647892</v>
       </c>
       <c r="L17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.06648916123669923</v>
+        <v>-0.08425672573086003</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.02522494392780352</v>
+        <v>-0.06334587307873651</v>
       </c>
       <c r="P17" t="n">
         <v>-0</v>
@@ -9588,49 +9588,49 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.01906094125911958</v>
+        <v>0.06023724467500365</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.004191752753759134</v>
+        <v>-0.05267309116892206</v>
       </c>
       <c r="X17" t="n">
-        <v>0.01180110368614054</v>
+        <v>0.002023197367531834</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.003272045536479402</v>
+        <v>-0.01760236852532795</v>
       </c>
       <c r="AD17" t="n">
         <v>-0</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.002587517684227683</v>
+        <v>-0.0577588608007779</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.00231735278533981</v>
+        <v>0.005667795359072101</v>
       </c>
       <c r="AH17" t="n">
         <v>-0</v>
@@ -9642,37 +9642,37 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.01806452962940453</v>
+        <v>0.01907790185305228</v>
       </c>
       <c r="AM17" t="n">
         <v>-0</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.01243386786388016</v>
+        <v>-0.03279324789573839</v>
       </c>
       <c r="AP17" t="n">
-        <v>-0.01228520317475038</v>
+        <v>0.006009324699997425</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.09027327901085329</v>
+        <v>0.2047505535943754</v>
       </c>
       <c r="AV17" t="n">
         <v>-0</v>
@@ -9681,25 +9681,25 @@
         <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>-0.05113521881706509</v>
+        <v>-0.122566255077423</v>
       </c>
       <c r="AY17" t="n">
-        <v>-0.01129680401635391</v>
+        <v>-0.0875325502405213</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA17" t="n">
         <v>-0</v>
       </c>
       <c r="BB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.01919559861795131</v>
+        <v>-0.02164178361000426</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
@@ -9708,64 +9708,64 @@
         <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.04969339796314527</v>
+        <v>-0.01232337492912886</v>
       </c>
       <c r="BH17" t="n">
-        <v>-0.01919363218217901</v>
+        <v>-0.00444542915371853</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
         <v>0</v>
       </c>
       <c r="BL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.02558812258889233</v>
+        <v>0.03142857731603116</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.01396521779819443</v>
+        <v>0.05551157567144697</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.0217762928690108</v>
+        <v>0.002868336026333868</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
         <v>-0</v>
       </c>
       <c r="BT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.04866710589721925</v>
+        <v>0.1262015038498201</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX17" t="n">
         <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>-0.02364773077474541</v>
+        <v>-0.04144153277037738</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.001996118077983738</v>
+        <v>-0.02918084037244212</v>
       </c>
       <c r="CA17" t="n">
         <v>-0</v>
@@ -9780,34 +9780,34 @@
         <v>0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.01760819412881975</v>
+        <v>-0.04432926185321448</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG17" t="n">
         <v>-0</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.01222752609177812</v>
+        <v>0.02828454650189088</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.007245793073079688</v>
+        <v>0.02244905793340447</v>
       </c>
       <c r="CJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK17" t="n">
         <v>-0</v>
       </c>
       <c r="CL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM17" t="n">
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.0002141957200115257</v>
+        <v>-0.0318874636945167</v>
       </c>
       <c r="CO17" t="n">
         <v>-0</v>
@@ -9816,40 +9816,40 @@
         <v>-0</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.003925178938257989</v>
+        <v>0.05526558969804204</v>
       </c>
       <c r="CR17" t="n">
-        <v>-0.003646202967627068</v>
+        <v>0.01671105001416602</v>
       </c>
       <c r="CS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV17" t="n">
         <v>-0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.01094687758772159</v>
+        <v>-0.04542752808449991</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
         <v>0</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.009415954308945634</v>
+        <v>0.02493848444848961</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.01312032000253682</v>
+        <v>0.03762893299077263</v>
       </c>
       <c r="DB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC17" t="n">
         <v>0</v>
@@ -9861,19 +9861,19 @@
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.01631896342086048</v>
+        <v>-0.03983530717061545</v>
       </c>
       <c r="DG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.01846983431862562</v>
+        <v>-0.04095832388797412</v>
       </c>
       <c r="DJ17" t="n">
-        <v>-0.003693580578417738</v>
+        <v>0.0159250373701761</v>
       </c>
       <c r="DK17" t="n">
         <v>0</v>
@@ -9882,40 +9882,40 @@
         <v>-0</v>
       </c>
       <c r="DM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN17" t="n">
         <v>-0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.008041331963759196</v>
+        <v>0.007897533915924355</v>
       </c>
       <c r="DP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.01979462192430372</v>
+        <v>-0.02882831525024543</v>
       </c>
       <c r="DS17" t="n">
-        <v>-0.01366813514594768</v>
+        <v>-0.001330311087722285</v>
       </c>
       <c r="DT17" t="n">
         <v>-0</v>
       </c>
       <c r="DU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>-0.01512565863019831</v>
+        <v>-0.01099574836975101</v>
       </c>
       <c r="DY17" t="n">
         <v>0</v>
@@ -9924,16 +9924,16 @@
         <v>-0</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.01340477666797229</v>
+        <v>-0.01852168617847985</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.001415198527650156</v>
+        <v>-0.001732339243399531</v>
       </c>
       <c r="EC17" t="n">
         <v>-0</v>
       </c>
       <c r="ED17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE17" t="n">
         <v>-0</v>
@@ -9942,22 +9942,22 @@
         <v>0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.01793955233745228</v>
+        <v>-0.0262911255668647</v>
       </c>
       <c r="EH17" t="n">
         <v>-0</v>
       </c>
       <c r="EI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.01082317761302391</v>
+        <v>0.02437037433461773</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.007110880765519101</v>
+        <v>0.0006051399637435671</v>
       </c>
       <c r="EL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM17" t="n">
         <v>-0</v>
@@ -9969,19 +9969,19 @@
         <v>0</v>
       </c>
       <c r="EP17" t="n">
-        <v>0.0003538967037369907</v>
+        <v>-0.03077126215995603</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.008469124541862586</v>
+        <v>0.02736314960902176</v>
       </c>
       <c r="ET17" t="n">
-        <v>-0.001591717708135629</v>
+        <v>0.05143346906447127</v>
       </c>
       <c r="EU17" t="n">
         <v>0</v>
@@ -9990,25 +9990,25 @@
         <v>0</v>
       </c>
       <c r="EW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX17" t="n">
         <v>0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.01113163272902852</v>
+        <v>-0.05209393238056755</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA17" t="n">
         <v>-0</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.01147713504073795</v>
+        <v>0.01799644510432529</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.0145324386488448</v>
+        <v>0.02306254443938176</v>
       </c>
       <c r="FD17" t="n">
         <v>0</v>
@@ -10020,10 +10020,10 @@
         <v>-0</v>
       </c>
       <c r="FG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH17" t="n">
-        <v>-0.002715196563887185</v>
+        <v>0.05484359754724453</v>
       </c>
       <c r="FI17" t="n">
         <v>-0</v>
@@ -10032,16 +10032,16 @@
         <v>-0</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.01351145408553161</v>
+        <v>-0.03642639001315871</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.01047446064001669</v>
+        <v>0.04090037014279284</v>
       </c>
       <c r="FM17" t="n">
         <v>0</v>
       </c>
       <c r="FN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO17" t="n">
         <v>0</v>
@@ -10050,52 +10050,52 @@
         <v>0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>-0.002701188916824334</v>
+        <v>-0.0167414066059839</v>
       </c>
       <c r="FR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS17" t="n">
         <v>-0</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.008326859423344778</v>
+        <v>0.02974479920288671</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.0120175413229906</v>
+        <v>-0.03288490210535657</v>
       </c>
       <c r="FV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>-0.0005504205876127753</v>
+        <v>-0.04698836091928854</v>
       </c>
       <c r="GA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB17" t="n">
         <v>-0</v>
       </c>
       <c r="GC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0.01311505274425613</v>
+        <v>0.04041042830583202</v>
       </c>
       <c r="GE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG17" t="n">
         <v>0</v>
@@ -10106,46 +10106,46 @@
         <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>0.4153572051450508</v>
+        <v>0.2561772895102798</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1527524371230786</v>
+        <v>-0.1750014830929682</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.05337349798471756</v>
+        <v>-0.01707228129826151</v>
       </c>
       <c r="F18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>-0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3239443995061827</v>
+        <v>0.3310243202847041</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1895680220001493</v>
+        <v>-0.2530986344472804</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.06892823910276677</v>
+        <v>-0.07292901125943244</v>
       </c>
       <c r="O18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>-0</v>
@@ -10157,22 +10157,22 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.102082386197136</v>
+        <v>0.05356350450260748</v>
       </c>
       <c r="U18" t="n">
         <v>-0</v>
       </c>
       <c r="V18" t="n">
-        <v>0.01067781167138243</v>
+        <v>-0.04687319317016449</v>
       </c>
       <c r="W18" t="n">
-        <v>0.09840651620137804</v>
+        <v>-0.03705709661439411</v>
       </c>
       <c r="X18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>-0</v>
@@ -10181,49 +10181,49 @@
         <v>-0</v>
       </c>
       <c r="AA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>-0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.1042984366478261</v>
+        <v>-0.0168642603143915</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.008280249905984419</v>
+        <v>-0.02899412825898812</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.007868876847546148</v>
+        <v>-0.0150814432286299</v>
       </c>
       <c r="AG18" t="n">
         <v>-0</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>-0.01413306067264882</v>
+        <v>0.05757216167317508</v>
       </c>
       <c r="AM18" t="n">
         <v>-0</v>
       </c>
       <c r="AN18" t="n">
-        <v>-0.06963297121984609</v>
+        <v>-0.06238822091384541</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.09327890535983155</v>
+        <v>0.03596742762678435</v>
       </c>
       <c r="AP18" t="n">
         <v>0</v>
@@ -10235,31 +10235,31 @@
         <v>-0</v>
       </c>
       <c r="AS18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.3350417824791784</v>
+        <v>0.2404149541552711</v>
       </c>
       <c r="AV18" t="n">
         <v>-0</v>
       </c>
       <c r="AW18" t="n">
-        <v>-0.0582899494006054</v>
+        <v>-0.145423785059637</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.1352134909149114</v>
+        <v>-0.1338746695358506</v>
       </c>
       <c r="AY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
         <v>-0</v>
       </c>
       <c r="BA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
         <v>-0</v>
@@ -10268,25 +10268,25 @@
         <v>-0</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.03028057937233576</v>
+        <v>-0.007752149394776846</v>
       </c>
       <c r="BE18" t="n">
         <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>-0.06014711045112877</v>
+        <v>-0.04414746632039725</v>
       </c>
       <c r="BG18" t="n">
-        <v>-0.1089048352468886</v>
+        <v>0.02384365208788119</v>
       </c>
       <c r="BH18" t="n">
         <v>0</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK18" t="n">
         <v>0</v>
@@ -10295,16 +10295,16 @@
         <v>-0</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.05861349550282345</v>
+        <v>-0.0008410011251675629</v>
       </c>
       <c r="BN18" t="n">
         <v>-0</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.0575667306426512</v>
+        <v>0.09645894003761352</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.1982779608751278</v>
+        <v>0.01307952018555015</v>
       </c>
       <c r="BQ18" t="n">
         <v>-0</v>
@@ -10316,55 +10316,55 @@
         <v>-0</v>
       </c>
       <c r="BT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU18" t="n">
         <v>-0</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.1635072823828878</v>
+        <v>0.1698814881300876</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX18" t="n">
-        <v>0.01661427909170024</v>
+        <v>-0.1458391754460469</v>
       </c>
       <c r="BY18" t="n">
-        <v>0.09747195118235644</v>
+        <v>-0.005598778551234183</v>
       </c>
       <c r="BZ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA18" t="n">
         <v>-0</v>
       </c>
       <c r="CB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE18" t="n">
-        <v>-0.09299382153137263</v>
+        <v>-0.07666697059516209</v>
       </c>
       <c r="CF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG18" t="n">
-        <v>0.02466341910762236</v>
+        <v>0.1084906814593476</v>
       </c>
       <c r="CH18" t="n">
-        <v>-0.01222205628045068</v>
+        <v>0.008496451031540524</v>
       </c>
       <c r="CI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK18" t="n">
         <v>0</v>
@@ -10376,49 +10376,49 @@
         <v>0</v>
       </c>
       <c r="CN18" t="n">
-        <v>-0.03087720610851103</v>
+        <v>-0.07823351359508972</v>
       </c>
       <c r="CO18" t="n">
         <v>-0</v>
       </c>
       <c r="CP18" t="n">
-        <v>-0.07622409350281764</v>
+        <v>0.1166813786195598</v>
       </c>
       <c r="CQ18" t="n">
-        <v>-0.136309073103893</v>
+        <v>0.04055031482710982</v>
       </c>
       <c r="CR18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS18" t="n">
         <v>-0</v>
       </c>
       <c r="CT18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW18" t="n">
-        <v>-0.08923844109489036</v>
+        <v>-0.08682244662341965</v>
       </c>
       <c r="CX18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY18" t="n">
-        <v>0.04471339974487957</v>
+        <v>0.1254738101017041</v>
       </c>
       <c r="CZ18" t="n">
-        <v>-0.004810092314039812</v>
+        <v>0.01084953685973634</v>
       </c>
       <c r="DA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC18" t="n">
         <v>-0</v>
@@ -10430,16 +10430,16 @@
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>-0.008880697775690335</v>
+        <v>-0.02695985563480279</v>
       </c>
       <c r="DG18" t="n">
         <v>0</v>
       </c>
       <c r="DH18" t="n">
-        <v>0.003708755479479001</v>
+        <v>0.01093239612189692</v>
       </c>
       <c r="DI18" t="n">
-        <v>-0.002878872980683219</v>
+        <v>-0.03487059043924402</v>
       </c>
       <c r="DJ18" t="n">
         <v>-0</v>
@@ -10454,22 +10454,22 @@
         <v>0</v>
       </c>
       <c r="DN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>-0.01040306623990542</v>
+        <v>-0.07519457440914891</v>
       </c>
       <c r="DP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ18" t="n">
-        <v>-0.1684177412083869</v>
+        <v>0.0438662129144749</v>
       </c>
       <c r="DR18" t="n">
-        <v>-0.03684732392055023</v>
+        <v>0.01566541962965003</v>
       </c>
       <c r="DS18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT18" t="n">
         <v>-0</v>
@@ -10478,82 +10478,82 @@
         <v>-0</v>
       </c>
       <c r="DV18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX18" t="n">
-        <v>-0.06528869013948503</v>
+        <v>-0.003432475501874451</v>
       </c>
       <c r="DY18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ18" t="n">
-        <v>0.01647540544408062</v>
+        <v>-0.01314104424326174</v>
       </c>
       <c r="EA18" t="n">
-        <v>0.01696301540797479</v>
+        <v>-0.03449910040350194</v>
       </c>
       <c r="EB18" t="n">
         <v>0</v>
       </c>
       <c r="EC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG18" t="n">
-        <v>-0.1170385087711713</v>
+        <v>-0.05154199724513816</v>
       </c>
       <c r="EH18" t="n">
         <v>0</v>
       </c>
       <c r="EI18" t="n">
-        <v>0.08252476119456385</v>
+        <v>0.07848901072739527</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.07755929381076397</v>
+        <v>0.0348342930062163</v>
       </c>
       <c r="EK18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM18" t="n">
         <v>-0</v>
       </c>
       <c r="EN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP18" t="n">
-        <v>-0.08683023244737859</v>
+        <v>-0.02209216035294274</v>
       </c>
       <c r="EQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER18" t="n">
-        <v>0.06773080070714632</v>
+        <v>0.07825511185941922</v>
       </c>
       <c r="ES18" t="n">
-        <v>0.01989386463468211</v>
+        <v>-0.01497028819188232</v>
       </c>
       <c r="ET18" t="n">
         <v>0</v>
       </c>
       <c r="EU18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV18" t="n">
         <v>0</v>
@@ -10562,46 +10562,46 @@
         <v>-0</v>
       </c>
       <c r="EX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY18" t="n">
-        <v>-0.08395258427681976</v>
+        <v>-0.09368032424183863</v>
       </c>
       <c r="EZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA18" t="n">
-        <v>0.02768983226285621</v>
+        <v>0.123554136443522</v>
       </c>
       <c r="FB18" t="n">
-        <v>-0.004075162106430106</v>
+        <v>0.01331652200640048</v>
       </c>
       <c r="FC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD18" t="n">
         <v>0</v>
       </c>
       <c r="FE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF18" t="n">
         <v>-0</v>
       </c>
       <c r="FG18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH18" t="n">
-        <v>-0.02981761782796473</v>
+        <v>0.0692475196620234</v>
       </c>
       <c r="FI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ18" t="n">
-        <v>-0.07811525575997685</v>
+        <v>-0.1447210542788393</v>
       </c>
       <c r="FK18" t="n">
-        <v>0.03957293323877484</v>
+        <v>0.01484784457313872</v>
       </c>
       <c r="FL18" t="n">
         <v>-0</v>
@@ -10613,22 +10613,22 @@
         <v>0</v>
       </c>
       <c r="FO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>-0.006028435789170863</v>
+        <v>-0.04293328085521802</v>
       </c>
       <c r="FR18" t="n">
         <v>-0</v>
       </c>
       <c r="FS18" t="n">
-        <v>0.1084392961027306</v>
+        <v>0.07866008797769514</v>
       </c>
       <c r="FT18" t="n">
-        <v>-0.005669346021173258</v>
+        <v>0.03681617316414271</v>
       </c>
       <c r="FU18" t="n">
         <v>-0</v>
@@ -10637,37 +10637,37 @@
         <v>0</v>
       </c>
       <c r="FW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX18" t="n">
         <v>0</v>
       </c>
       <c r="FY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>0.01330668224531322</v>
+        <v>-0.0165711092709719</v>
       </c>
       <c r="GA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB18" t="n">
-        <v>-0.0646767419494222</v>
+        <v>0.0345974475000691</v>
       </c>
       <c r="GC18" t="n">
         <v>-0</v>
       </c>
       <c r="GD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -11244,19 +11244,19 @@
         <v>0</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1955844602962666</v>
+        <v>0.7878633203216263</v>
       </c>
       <c r="C20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0573237275039872</v>
+        <v>0.1753757439169801</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1176689356884328</v>
+        <v>-0.2848025707500379</v>
       </c>
       <c r="G20" t="n">
         <v>-0</v>
@@ -11265,40 +11265,40 @@
         <v>-0</v>
       </c>
       <c r="I20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1725380383146246</v>
+        <v>1.052020991432592</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.03145811373663959</v>
+        <v>-0.02868449116591235</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1173016771310044</v>
+        <v>-0.2635062595567315</v>
       </c>
       <c r="P20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.02088460486761182</v>
+        <v>0.2079886283190378</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -11307,16 +11307,16 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.01640005628446425</v>
+        <v>-0.08988934089694015</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.001993725783814916</v>
+        <v>-0.03733567909227709</v>
       </c>
       <c r="Y20" t="n">
         <v>-0</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -11325,22 +11325,22 @@
         <v>-0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.001356453217562624</v>
+        <v>0.02773102369761076</v>
       </c>
       <c r="AD20" t="n">
         <v>-0</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.01935586411750067</v>
+        <v>-0.3836868560917128</v>
       </c>
       <c r="AG20" t="n">
-        <v>-0.0002807767392033485</v>
+        <v>-0.06763825322011548</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>-0</v>
@@ -11352,7 +11352,7 @@
         <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.02453327275050268</v>
+        <v>0.1946461235988402</v>
       </c>
       <c r="AM20" t="n">
         <v>0</v>
@@ -11361,10 +11361,10 @@
         <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.004011956251488029</v>
+        <v>0.004040885704422371</v>
       </c>
       <c r="AP20" t="n">
-        <v>-0.03186811951592929</v>
+        <v>-0.088055344967441</v>
       </c>
       <c r="AQ20" t="n">
         <v>-0</v>
@@ -11376,10 +11376,10 @@
         <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.1182207341344241</v>
+        <v>0.9356747488995848</v>
       </c>
       <c r="AV20" t="n">
         <v>-0</v>
@@ -11388,79 +11388,79 @@
         <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>-0.01706000986491803</v>
+        <v>-0.2145807810634514</v>
       </c>
       <c r="AY20" t="n">
-        <v>-0.0622545558779858</v>
+        <v>-0.1358086835724432</v>
       </c>
       <c r="AZ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
         <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD20" t="n">
-        <v>0.03487884350627186</v>
+        <v>-0.09620385774168327</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF20" t="n">
         <v>0</v>
       </c>
       <c r="BG20" t="n">
-        <v>-0.04686936049584645</v>
+        <v>-0.1128013532478385</v>
       </c>
       <c r="BH20" t="n">
-        <v>-0.04431923995765664</v>
+        <v>-0.1497521574502735</v>
       </c>
       <c r="BI20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL20" t="n">
         <v>-0</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.03312529975264238</v>
+        <v>0.1497531676924427</v>
       </c>
       <c r="BN20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO20" t="n">
         <v>-0</v>
       </c>
       <c r="BP20" t="n">
-        <v>0.003557253501918739</v>
+        <v>0.02932298932774973</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0.01915244502906337</v>
+        <v>-0.04570139209666776</v>
       </c>
       <c r="BR20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS20" t="n">
         <v>0</v>
       </c>
       <c r="BT20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU20" t="n">
         <v>0</v>
       </c>
       <c r="BV20" t="n">
-        <v>0.0602171278281084</v>
+        <v>0.5668626715363552</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
@@ -11469,10 +11469,10 @@
         <v>0</v>
       </c>
       <c r="BY20" t="n">
-        <v>-0.01864234103097717</v>
+        <v>-0.03867182932408814</v>
       </c>
       <c r="BZ20" t="n">
-        <v>-0.04035080286368642</v>
+        <v>-0.1926619328002012</v>
       </c>
       <c r="CA20" t="n">
         <v>-0</v>
@@ -11487,154 +11487,154 @@
         <v>-0</v>
       </c>
       <c r="CE20" t="n">
-        <v>-0.03091895479689228</v>
+        <v>-0.2621310381608715</v>
       </c>
       <c r="CF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG20" t="n">
         <v>-0</v>
       </c>
       <c r="CH20" t="n">
-        <v>-0.002999741711921904</v>
+        <v>0.03875378378788715</v>
       </c>
       <c r="CI20" t="n">
-        <v>0.02745837148458497</v>
+        <v>0.1125435231158723</v>
       </c>
       <c r="CJ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK20" t="n">
         <v>0</v>
       </c>
       <c r="CL20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM20" t="n">
         <v>0</v>
       </c>
       <c r="CN20" t="n">
-        <v>0.00736323709553628</v>
+        <v>-0.4206053496293856</v>
       </c>
       <c r="CO20" t="n">
         <v>-0</v>
       </c>
       <c r="CP20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ20" t="n">
-        <v>-0.01337612968087371</v>
+        <v>0.2412518257946932</v>
       </c>
       <c r="CR20" t="n">
-        <v>-0.008538606990017008</v>
+        <v>0.1373299599268796</v>
       </c>
       <c r="CS20" t="n">
         <v>-0</v>
       </c>
       <c r="CT20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW20" t="n">
-        <v>-0.02406000500622384</v>
+        <v>-0.2355637327233895</v>
       </c>
       <c r="CX20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY20" t="n">
         <v>0</v>
       </c>
       <c r="CZ20" t="n">
-        <v>-0.006775498304454394</v>
+        <v>-0.02538272437477521</v>
       </c>
       <c r="DA20" t="n">
-        <v>0.03280272960414036</v>
+        <v>0.144313813824928</v>
       </c>
       <c r="DB20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC20" t="n">
         <v>-0</v>
       </c>
       <c r="DD20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF20" t="n">
-        <v>-0.01228768337052847</v>
+        <v>-0.05974332068089105</v>
       </c>
       <c r="DG20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.03094020918752625</v>
+        <v>-0.3772494412608997</v>
       </c>
       <c r="DJ20" t="n">
-        <v>0.0001226839614979743</v>
+        <v>0.0705458071498398</v>
       </c>
       <c r="DK20" t="n">
         <v>0</v>
       </c>
       <c r="DL20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO20" t="n">
-        <v>-0.006795211005618329</v>
+        <v>-0.1019115115004232</v>
       </c>
       <c r="DP20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ20" t="n">
         <v>0</v>
       </c>
       <c r="DR20" t="n">
-        <v>0.0307923293361752</v>
+        <v>0.0009387559614029015</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.0004612995519719142</v>
+        <v>-0.03777027794315943</v>
       </c>
       <c r="DT20" t="n">
         <v>-0</v>
       </c>
       <c r="DU20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW20" t="n">
         <v>-0</v>
       </c>
       <c r="DX20" t="n">
-        <v>-0.01377460250652974</v>
+        <v>-0.03195515761340013</v>
       </c>
       <c r="DY20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ20" t="n">
         <v>-0</v>
       </c>
       <c r="EA20" t="n">
-        <v>-0.004741634155976387</v>
+        <v>-0.2125355220908846</v>
       </c>
       <c r="EB20" t="n">
-        <v>0.01780713693393893</v>
+        <v>0.1005985311688274</v>
       </c>
       <c r="EC20" t="n">
         <v>-0</v>
@@ -11646,37 +11646,37 @@
         <v>-0</v>
       </c>
       <c r="EF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG20" t="n">
-        <v>-0.03293124787782795</v>
+        <v>-0.06804950097864934</v>
       </c>
       <c r="EH20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI20" t="n">
         <v>0</v>
       </c>
       <c r="EJ20" t="n">
-        <v>0.00304971769285448</v>
+        <v>-0.1232623316891327</v>
       </c>
       <c r="EK20" t="n">
-        <v>0.02741264553479034</v>
+        <v>0.0244671423088197</v>
       </c>
       <c r="EL20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM20" t="n">
         <v>-0</v>
       </c>
       <c r="EN20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO20" t="n">
         <v>0</v>
       </c>
       <c r="EP20" t="n">
-        <v>-0.01162491910939762</v>
+        <v>-0.05713902585655186</v>
       </c>
       <c r="EQ20" t="n">
         <v>0</v>
@@ -11685,70 +11685,70 @@
         <v>-0</v>
       </c>
       <c r="ES20" t="n">
-        <v>-0.01449646432241165</v>
+        <v>-0.1078659820456623</v>
       </c>
       <c r="ET20" t="n">
-        <v>0.01451631036138486</v>
+        <v>0.04829185494511695</v>
       </c>
       <c r="EU20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY20" t="n">
-        <v>-0.02235811953906987</v>
+        <v>-0.2770526568463335</v>
       </c>
       <c r="EZ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA20" t="n">
         <v>-0</v>
       </c>
       <c r="FB20" t="n">
-        <v>-0.004649318084795771</v>
+        <v>-0.06955994564503337</v>
       </c>
       <c r="FC20" t="n">
-        <v>0.03077857441642638</v>
+        <v>0.1307979196548326</v>
       </c>
       <c r="FD20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE20" t="n">
         <v>0</v>
       </c>
       <c r="FF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH20" t="n">
-        <v>0.002722592043912259</v>
+        <v>0.3173173310531133</v>
       </c>
       <c r="FI20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ20" t="n">
         <v>-0</v>
       </c>
       <c r="FK20" t="n">
-        <v>0.008630068950705883</v>
+        <v>-0.1927178963482096</v>
       </c>
       <c r="FL20" t="n">
-        <v>-0.02239772934934034</v>
+        <v>-0.2770468636342763</v>
       </c>
       <c r="FM20" t="n">
         <v>0</v>
       </c>
       <c r="FN20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO20" t="n">
         <v>0</v>
@@ -11757,7 +11757,7 @@
         <v>0</v>
       </c>
       <c r="FQ20" t="n">
-        <v>-0.003555128235483988</v>
+        <v>-0.1569485778581266</v>
       </c>
       <c r="FR20" t="n">
         <v>-0</v>
@@ -11766,46 +11766,46 @@
         <v>-0</v>
       </c>
       <c r="FT20" t="n">
-        <v>0.003938254028870664</v>
+        <v>0.07158514427785638</v>
       </c>
       <c r="FU20" t="n">
-        <v>0.03465978461921009</v>
+        <v>-0.2219408003871606</v>
       </c>
       <c r="FV20" t="n">
         <v>-0</v>
       </c>
       <c r="FW20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ20" t="n">
-        <v>0.01840337407645683</v>
+        <v>0.02764576239744682</v>
       </c>
       <c r="GA20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB20" t="n">
         <v>-0</v>
       </c>
       <c r="GC20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD20" t="n">
-        <v>-0.01639096137968626</v>
+        <v>0.05844353895394877</v>
       </c>
       <c r="GE20" t="n">
         <v>-0</v>
       </c>
       <c r="GF20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
